--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f4a70b6a4b54cab/Documente/Semestrul_6/VVSS/Proiect/docs/Lab01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D906EE69-AC8E-4A3E-9BE0-73DC573C23FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{D906EE69-AC8E-4A3E-9BE0-73DC573C23FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F14D6AE1-A764-4AFC-8F80-513228CCCBAE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="126">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -412,6 +412,18 @@
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (minutes):</t>
+  </si>
+  <si>
+    <t>01.03.2026</t>
+  </si>
+  <si>
+    <t>Agoston Nikolett, Bercea Cristian</t>
+  </si>
+  <si>
+    <t>02.03.2026</t>
+  </si>
+  <si>
+    <t>SonarQube</t>
   </si>
 </sst>
 </file>
@@ -655,6 +667,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -697,13 +716,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,10 +731,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1034,19 +1042,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -1070,10 +1078,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="31"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
@@ -1088,10 +1096,10 @@
       <c r="C5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="33"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -1103,15 +1111,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="28"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
@@ -1363,19 +1375,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -1399,10 +1411,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
@@ -1417,10 +1429,10 @@
       <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="36"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -1432,15 +1444,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="28"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
@@ -1716,19 +1732,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -1752,10 +1768,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="34"/>
+      <c r="E4" s="37"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
@@ -1770,10 +1786,10 @@
       <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="39"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -1785,15 +1801,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="D7" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="28"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
@@ -2112,19 +2132,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>29</v>
@@ -2137,7 +2157,7 @@
       <c r="H3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="25" t="s">
         <v>31</v>
       </c>
       <c r="J3" s="17">
@@ -2148,12 +2168,14 @@
       <c r="C4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="D4" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="37"/>
       <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="25" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="3">
@@ -2164,8 +2186,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
+      <c r="D5" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="28"/>
       <c r="H5" s="17" t="s">
         <v>21</v>
       </c>
@@ -2177,8 +2201,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="D6" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="28"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -2208,10 +2234,10 @@
       <c r="D10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="26" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2220,16 +2246,16 @@
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="26" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2238,16 +2264,16 @@
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="26" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2256,14 +2282,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2272,16 +2298,16 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="26" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2290,140 +2316,140 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="3">
@@ -2446,11 +2472,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
       <c r="F32" s="18">
         <v>30</v>
       </c>
